--- a/document/タスク編集画面_ユースケース.xlsx
+++ b/document/タスク編集画面_ユースケース.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B05DA80-B76A-432E-94F2-7EF9BC892001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5072C0F-E540-4A50-B28F-5897FCA44D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -298,8 +298,40 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>なし</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員がメニュー画面を表示する。
+2.従業員が「一覧表示」を選択する。
+3.従業員が編集したいレコードのラジオボタンを選択する。
+4.従業員が「編集」をを選択する。
+5.従業員がタスク編集画面にて、以下の情報を入力する。
+①タスク名　②カテゴリ情報　③期限　④担当者情報　⑤ステータス情報　⑥メモ(空欄可)
+6.タスクの編集が完了する。</t>
+    <rPh sb="40" eb="43">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="69" eb="72">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>E1.タスクが1つも存在しない場合
-E1-1.編集するタスクを選択する際に「タスクが存在しません」と表示される
+E1-1.タスク一覧表示画面で「タスクが存在しません」と表示される
 E2.システムエラーが発生した場合
 E2-2.「システムエラーが発生しました」と表示</t>
     <rPh sb="10" eb="12">
@@ -308,68 +340,33 @@
     <rPh sb="15" eb="17">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="23" eb="25">
-      <t>ヘンシュウ</t>
+    <rPh sb="26" eb="28">
+      <t>イチラン</t>
     </rPh>
-    <rPh sb="31" eb="33">
-      <t>センタク</t>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="35" eb="36">
-      <t>サイ</t>
+    <rPh sb="30" eb="32">
+      <t>ガメン</t>
     </rPh>
-    <rPh sb="42" eb="44">
+    <rPh sb="38" eb="40">
       <t>ソンザイ</t>
     </rPh>
-    <rPh sb="50" eb="52">
+    <rPh sb="46" eb="48">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="68" eb="70">
+    <rPh sb="64" eb="66">
       <t>ハッセイ</t>
     </rPh>
-    <rPh sb="72" eb="74">
+    <rPh sb="68" eb="70">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="89" eb="91">
+    <rPh sb="85" eb="87">
       <t>ハッセイ</t>
     </rPh>
-    <rPh sb="97" eb="99">
+    <rPh sb="93" eb="95">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>なし</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <r>
-      <t>1.従業員がメニュー画面を表示する。
-2.従業員が「一覧表示」を選択する。
-3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS PGothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>T.B.D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-4.従業員がタスク編集画面にて、以下の情報を入力する。
-①タスク名　②カテゴリ情報　③期限　④担当者情報　⑤ステータス情報　⑥メモ(空欄可)
-5.タスクの編集が完了する。</t>
-    </r>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -380,7 +377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -442,13 +439,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="MS PGothic"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2966,7 +2956,7 @@
       <c r="I8" s="45"/>
       <c r="J8" s="46"/>
     </row>
-    <row r="9" spans="1:10" ht="86.25" customHeight="1">
+    <row r="9" spans="1:10" ht="100.5" customHeight="1">
       <c r="A9" s="63" t="s">
         <v>13</v>
       </c>
@@ -2975,7 +2965,7 @@
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="45"/>
       <c r="F9" s="45"/>
@@ -2991,7 +2981,7 @@
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="45"/>
@@ -3007,7 +2997,7 @@
       </c>
       <c r="C11" s="62"/>
       <c r="D11" s="47" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" s="45"/>
       <c r="F11" s="45"/>
@@ -3039,7 +3029,7 @@
       <c r="B13" s="39"/>
       <c r="C13" s="49"/>
       <c r="D13" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>

--- a/document/タスク編集画面_ユースケース.xlsx
+++ b/document/タスク編集画面_ユースケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5072C0F-E540-4A50-B28F-5897FCA44D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43D0D35-161E-42BE-839D-34165FCE2511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -248,29 +248,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク編集</t>
-    <rPh sb="3" eb="5">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>従業員</t>
     <rPh sb="0" eb="3">
       <t>ジュウギョウイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>すでにタスク管理システムに登録されているタスクを編集する</t>
-    <rPh sb="6" eb="8">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -302,70 +282,132 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.従業員がメニュー画面を表示する。
-2.従業員が「一覧表示」を選択する。
-3.従業員が編集したいレコードのラジオボタンを選択する。
-4.従業員が「編集」をを選択する。
-5.従業員がタスク編集画面にて、以下の情報を入力する。
+    <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集する</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コショウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集する</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員はメニュー画面を表示する。
+2.従業員は「一覧表示」を選択する。
+3.従業員は編集したいレコードに対応したラジオボタンを選択する。
+4.従業員は「編集」を選択する。
+5.タスク編集画面へ遷移する。
+6.従業員がタスク編集画面にて、以下の情報を入力する。
 ①タスク名　②カテゴリ情報　③期限　④担当者情報　⑤ステータス情報　⑥メモ(空欄可)
-6.タスクの編集が完了する。</t>
+7.タスクの編集が完了する。</t>
     <rPh sb="40" eb="43">
       <t>ジュウギョウイン</t>
     </rPh>
     <rPh sb="44" eb="46">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="61" eb="63">
+    <rPh sb="54" eb="56">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
       <t>センタク</t>
     </rPh>
-    <rPh sb="69" eb="72">
+    <rPh sb="73" eb="76">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="74" eb="76">
+    <rPh sb="78" eb="80">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="79" eb="81">
+    <rPh sb="82" eb="84">
       <t>センタク</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1.タスクが1つも存在しない場合
-E1-1.タスク一覧表示画面で「タスクが存在しません」と表示される
-E2.システムエラーが発生した場合
-E2-2.「システムエラーが発生しました」と表示</t>
-    <rPh sb="10" eb="12">
-      <t>ソンザイ</t>
+    <t>A1.タスクが1つも存在しない場合
+A1-1.タスク一覧表示画面で「タスクが存在しません」と表示される
+A2.従業員が未ログイン状態の場合
+A2-1.ログイン画面へ遷移する</t>
+    <rPh sb="56" eb="59">
+      <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="15" eb="17">
-      <t>バアイ</t>
+    <rPh sb="60" eb="61">
+      <t>ミ</t>
     </rPh>
-    <rPh sb="26" eb="28">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ハッセイ</t>
+    <rPh sb="65" eb="67">
+      <t>ジョウタイ</t>
     </rPh>
     <rPh sb="68" eb="70">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="85" eb="87">
-      <t>ハッセイ</t>
+    <rPh sb="80" eb="82">
+      <t>ガメン</t>
     </rPh>
-    <rPh sb="93" eb="95">
-      <t>ヒョウジ</t>
+    <rPh sb="83" eb="85">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1.データベース登録に失敗した場合
+E1-2.タスク編集失敗画面に遷移する</t>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -2899,7 +2941,7 @@
       <c r="B5" s="42"/>
       <c r="C5" s="60"/>
       <c r="D5" s="41" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E5" s="42"/>
       <c r="F5" s="42"/>
@@ -2915,7 +2957,7 @@
       <c r="B6" s="45"/>
       <c r="C6" s="62"/>
       <c r="D6" s="44" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E6" s="45"/>
       <c r="F6" s="45"/>
@@ -2931,7 +2973,7 @@
       <c r="B7" s="45"/>
       <c r="C7" s="62"/>
       <c r="D7" s="44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="45"/>
       <c r="F7" s="45"/>
@@ -2947,7 +2989,7 @@
       <c r="B8" s="45"/>
       <c r="C8" s="62"/>
       <c r="D8" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="45"/>
@@ -2956,7 +2998,7 @@
       <c r="I8" s="45"/>
       <c r="J8" s="46"/>
     </row>
-    <row r="9" spans="1:10" ht="100.5" customHeight="1">
+    <row r="9" spans="1:10" ht="125.25" customHeight="1">
       <c r="A9" s="63" t="s">
         <v>13</v>
       </c>
@@ -2981,7 +3023,7 @@
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="47" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="45"/>
@@ -2997,7 +3039,7 @@
       </c>
       <c r="C11" s="62"/>
       <c r="D11" s="47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="45"/>
       <c r="F11" s="45"/>
@@ -3013,7 +3055,7 @@
       <c r="B12" s="45"/>
       <c r="C12" s="62"/>
       <c r="D12" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12" s="45"/>
       <c r="F12" s="45"/>
@@ -3029,7 +3071,7 @@
       <c r="B13" s="39"/>
       <c r="C13" s="49"/>
       <c r="D13" s="38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
